--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_40c_bevNight75.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_40c_bevNight75.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339D306F-8878-4F40-BAFF-F38A18E7E686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9700587C-63CA-410A-A300-5B0D5717F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12494" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12801" uniqueCount="330">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -972,9 +972,6 @@
     <t>other_indexes</t>
   </si>
   <si>
-    <t>ncap_com</t>
-  </si>
-  <si>
     <t>DEF_C</t>
   </si>
   <si>
@@ -1030,6 +1027,12 @@
   </si>
   <si>
     <t>~UC_T: LO~2035</t>
+  </si>
+  <si>
+    <t>~TFM_DINS-AT</t>
+  </si>
+  <si>
+    <t>NCAP_COM</t>
   </si>
 </sst>
 </file>
@@ -1144,13 +1147,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Heading 2 2" xfId="2" xr:uid="{A6AB1C46-4E7B-4C21-A104-E4DF3FE4CE4A}"/>
@@ -1510,7 +1514,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -1519,19 +1523,19 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D11" t="s">
         <v>315</v>
-      </c>
-      <c r="D11" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D12" t="s">
         <v>317</v>
-      </c>
-      <c r="D12" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.45">
@@ -1646,7 +1650,7 @@
     </row>
     <row r="29" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="I29" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -50399,10 +50403,12 @@
         <f>IF(A11="x","DeActivated","~TFM_DINS-TSL: attribute=NCAP_PKCNT")</f>
         <v>~TFM_DINS-TSL: attribute=NCAP_PKCNT</v>
       </c>
-      <c r="FA9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
-      </c>
+      <c r="FA9" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="FB9" s="6"/>
+      <c r="FC9" s="6"/>
+      <c r="FD9" s="6"/>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
@@ -50858,17 +50864,17 @@
       <c r="EY10" t="s">
         <v>93</v>
       </c>
-      <c r="FA10" t="s">
+      <c r="FA10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="FB10" t="s">
+      <c r="FB10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="FC10" t="s">
+      <c r="FC10" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="FD10" t="s">
-        <v>309</v>
+      <c r="FD10" s="6" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="2:160" x14ac:dyDescent="0.45">
@@ -51325,17 +51331,17 @@
       <c r="EY11">
         <v>0</v>
       </c>
-      <c r="FA11" t="s">
-        <v>303</v>
-      </c>
-      <c r="FB11" t="s">
+      <c r="FA11" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="FB11" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC11" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="FC11" t="s">
-        <v>311</v>
-      </c>
-      <c r="FD11">
-        <v>0.24483753692114285</v>
+      <c r="FD11" s="6">
+        <v>0.51269413341068804</v>
       </c>
     </row>
     <row r="12" spans="2:160" x14ac:dyDescent="0.45">
@@ -51792,17 +51798,17 @@
       <c r="EY12">
         <v>0</v>
       </c>
-      <c r="FA12" t="s">
-        <v>305</v>
-      </c>
-      <c r="FB12" t="s">
+      <c r="FA12" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="FB12" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC12" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="FC12" t="s">
-        <v>311</v>
-      </c>
-      <c r="FD12">
-        <v>0.24483753692114285</v>
+      <c r="FD12" s="6">
+        <v>0.49829316177414618</v>
       </c>
     </row>
     <row r="13" spans="2:160" x14ac:dyDescent="0.45">
@@ -52259,17 +52265,17 @@
       <c r="EY13">
         <v>0</v>
       </c>
-      <c r="FA13" t="s">
-        <v>306</v>
-      </c>
-      <c r="FB13" t="s">
+      <c r="FA13" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="FB13" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC13" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="FC13" t="s">
-        <v>311</v>
-      </c>
-      <c r="FD13">
-        <v>0.24483753692114285</v>
+      <c r="FD13" s="6">
+        <v>0.47833276152748838</v>
       </c>
     </row>
     <row r="14" spans="2:160" x14ac:dyDescent="0.45">
@@ -52498,6 +52504,18 @@
       <c r="EY14">
         <v>0</v>
       </c>
+      <c r="FA14" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="FB14" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC14" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD14" s="6">
+        <v>0.53010270120310377</v>
+      </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -52725,6 +52743,18 @@
       <c r="EY15">
         <v>0</v>
       </c>
+      <c r="FA15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="FB15" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC15" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD15" s="6">
+        <v>0.51270487901899442</v>
+      </c>
     </row>
     <row r="16" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
@@ -52956,8 +52986,20 @@
       <c r="EY16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA16" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="FB16" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC16" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD16" s="6">
+        <v>0.54794780729860715</v>
+      </c>
+    </row>
+    <row r="17" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>204</v>
       </c>
@@ -53297,8 +53339,20 @@
       <c r="EY17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA17" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="FB17" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC17" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD17" s="6">
+        <v>0.53297669201702957</v>
+      </c>
+    </row>
+    <row r="18" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>205</v>
       </c>
@@ -53414,10 +53468,10 @@
         <v>0</v>
       </c>
       <c r="AO18" t="s">
+        <v>325</v>
+      </c>
+      <c r="AP18" t="s">
         <v>326</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>327</v>
       </c>
       <c r="AQ18">
         <v>3</v>
@@ -53638,8 +53692,20 @@
       <c r="EY18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="FB18" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC18" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD18" s="6">
+        <v>0.54562524626544517</v>
+      </c>
+    </row>
+    <row r="19" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>206</v>
       </c>
@@ -53865,8 +53931,20 @@
       <c r="EY19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA19" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="FB19" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC19" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD19" s="6">
+        <v>0.50977486126441274</v>
+      </c>
+    </row>
+    <row r="20" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>207</v>
       </c>
@@ -54092,8 +54170,20 @@
       <c r="EY20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="FB20" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC20" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD20" s="6">
+        <v>0.50323529625913033</v>
+      </c>
+    </row>
+    <row r="21" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>208</v>
       </c>
@@ -54319,8 +54409,20 @@
       <c r="EY21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA21" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="FB21" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC21" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD21" s="6">
+        <v>0.520902494297517</v>
+      </c>
+    </row>
+    <row r="22" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>209</v>
       </c>
@@ -54546,8 +54648,20 @@
       <c r="EY22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA22" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="FB22" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC22" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD22" s="6">
+        <v>0.4685610472250159</v>
+      </c>
+    </row>
+    <row r="23" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>210</v>
       </c>
@@ -54773,8 +54887,20 @@
       <c r="EY23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA23" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="FB23" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC23" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD23" s="6">
+        <v>0.50965105973602831</v>
+      </c>
+    </row>
+    <row r="24" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>211</v>
       </c>
@@ -55000,8 +55126,20 @@
       <c r="EY24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA24" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="FB24" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC24" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD24" s="6">
+        <v>0.51299283214720304</v>
+      </c>
+    </row>
+    <row r="25" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>212</v>
       </c>
@@ -55227,8 +55365,20 @@
       <c r="EY25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA25" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="FB25" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC25" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD25" s="6">
+        <v>0.4963617091927281</v>
+      </c>
+    </row>
+    <row r="26" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>213</v>
       </c>
@@ -55454,8 +55604,20 @@
       <c r="EY26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="FB26" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC26" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD26" s="6">
+        <v>0.4910168961480742</v>
+      </c>
+    </row>
+    <row r="27" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>214</v>
       </c>
@@ -55681,8 +55843,20 @@
       <c r="EY27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA27" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="FB27" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC27" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD27" s="6">
+        <v>0.48463453595850303</v>
+      </c>
+    </row>
+    <row r="28" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>215</v>
       </c>
@@ -55908,8 +56082,20 @@
       <c r="EY28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA28" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="FB28" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC28" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD28" s="6">
+        <v>0.53803013391388455</v>
+      </c>
+    </row>
+    <row r="29" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>216</v>
       </c>
@@ -56135,8 +56321,20 @@
       <c r="EY29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA29" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="FB29" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC29" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD29" s="6">
+        <v>0.57298848076496567</v>
+      </c>
+    </row>
+    <row r="30" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>217</v>
       </c>
@@ -56362,8 +56560,20 @@
       <c r="EY30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA30" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="FB30" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC30" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD30" s="6">
+        <v>0.50710280244884343</v>
+      </c>
+    </row>
+    <row r="31" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>218</v>
       </c>
@@ -56589,8 +56799,20 @@
       <c r="EY31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA31" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="FB31" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC31" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD31" s="6">
+        <v>0.48253152946703259</v>
+      </c>
+    </row>
+    <row r="32" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>219</v>
       </c>
@@ -56816,8 +57038,20 @@
       <c r="EY32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA32" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="FB32" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC32" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD32" s="6">
+        <v>0.43613332957741835</v>
+      </c>
+    </row>
+    <row r="33" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>220</v>
       </c>
@@ -57043,8 +57277,20 @@
       <c r="EY33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA33" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="FB33" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC33" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD33" s="6">
+        <v>0.44029113218195304</v>
+      </c>
+    </row>
+    <row r="34" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>221</v>
       </c>
@@ -57270,8 +57516,20 @@
       <c r="EY34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA34" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="FB34" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC34" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD34" s="6">
+        <v>0.46185715443059638</v>
+      </c>
+    </row>
+    <row r="35" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>222</v>
       </c>
@@ -57497,8 +57755,20 @@
       <c r="EY35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA35" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="FB35" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC35" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD35" s="6">
+        <v>0.4822687103353252</v>
+      </c>
+    </row>
+    <row r="36" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>223</v>
       </c>
@@ -57724,8 +57994,20 @@
       <c r="EY36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="FB36" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC36" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD36" s="6">
+        <v>0.50794409494845127</v>
+      </c>
+    </row>
+    <row r="37" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>224</v>
       </c>
@@ -57951,8 +58233,20 @@
       <c r="EY37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA37" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="FB37" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC37" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD37" s="6">
+        <v>0.48557434469558935</v>
+      </c>
+    </row>
+    <row r="38" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>225</v>
       </c>
@@ -58178,8 +58472,20 @@
       <c r="EY38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA38" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="FB38" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC38" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD38" s="6">
+        <v>0.44682174254294993</v>
+      </c>
+    </row>
+    <row r="39" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>226</v>
       </c>
@@ -58405,8 +58711,20 @@
       <c r="EY39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA39" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="FB39" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC39" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD39" s="6">
+        <v>0.44508960298044919</v>
+      </c>
+    </row>
+    <row r="40" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>227</v>
       </c>
@@ -58632,8 +58950,20 @@
       <c r="EY40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA40" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="FB40" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC40" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD40" s="6">
+        <v>0.46164545916235072</v>
+      </c>
+    </row>
+    <row r="41" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>228</v>
       </c>
@@ -58859,8 +59189,20 @@
       <c r="EY41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA41" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="FB41" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC41" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD41" s="6">
+        <v>0.38649512390673746</v>
+      </c>
+    </row>
+    <row r="42" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>229</v>
       </c>
@@ -59086,8 +59428,20 @@
       <c r="EY42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA42" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="FB42" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC42" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD42" s="6">
+        <v>0.42030934925103847</v>
+      </c>
+    </row>
+    <row r="43" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>230</v>
       </c>
@@ -59313,8 +59667,20 @@
       <c r="EY43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA43" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="FB43" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC43" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD43" s="6">
+        <v>0.45460198641246546</v>
+      </c>
+    </row>
+    <row r="44" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>231</v>
       </c>
@@ -59540,8 +59906,20 @@
       <c r="EY44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA44" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="FB44" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC44" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD44" s="6">
+        <v>0.48728452199187833</v>
+      </c>
+    </row>
+    <row r="45" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>232</v>
       </c>
@@ -59767,8 +60145,20 @@
       <c r="EY45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA45" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="FB45" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC45" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD45" s="6">
+        <v>0.4485587132476534</v>
+      </c>
+    </row>
+    <row r="46" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>233</v>
       </c>
@@ -59994,8 +60384,20 @@
       <c r="EY46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA46" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="FB46" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC46" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD46" s="6">
+        <v>0.52092576463639917</v>
+      </c>
+    </row>
+    <row r="47" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>234</v>
       </c>
@@ -60221,8 +60623,20 @@
       <c r="EY47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA47" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="FB47" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC47" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD47" s="6">
+        <v>0.50295734684982296</v>
+      </c>
+    </row>
+    <row r="48" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>235</v>
       </c>
@@ -60448,8 +60862,20 @@
       <c r="EY48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA48" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="FB48" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC48" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD48" s="6">
+        <v>0.51292468414888714</v>
+      </c>
+    </row>
+    <row r="49" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>236</v>
       </c>
@@ -60675,8 +61101,20 @@
       <c r="EY49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA49" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="FB49" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC49" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD49" s="6">
+        <v>0.52950898017118675</v>
+      </c>
+    </row>
+    <row r="50" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>237</v>
       </c>
@@ -60902,8 +61340,20 @@
       <c r="EY50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA50" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="FB50" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC50" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD50" s="6">
+        <v>0.51945692678441657</v>
+      </c>
+    </row>
+    <row r="51" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>238</v>
       </c>
@@ -61129,8 +61579,20 @@
       <c r="EY51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA51" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="FB51" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC51" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD51" s="6">
+        <v>0.53522770630033267</v>
+      </c>
+    </row>
+    <row r="52" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>239</v>
       </c>
@@ -61356,8 +61818,20 @@
       <c r="EY52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA52" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="FB52" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC52" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD52" s="6">
+        <v>0.53353471446184364</v>
+      </c>
+    </row>
+    <row r="53" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>240</v>
       </c>
@@ -61583,8 +62057,20 @@
       <c r="EY53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA53" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="FB53" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC53" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD53" s="6">
+        <v>0.51433171825744606</v>
+      </c>
+    </row>
+    <row r="54" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>241</v>
       </c>
@@ -61810,8 +62296,20 @@
       <c r="EY54">
         <v>0.56740472649949181</v>
       </c>
-    </row>
-    <row r="55" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA54" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="FB54" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC54" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD54" s="6">
+        <v>0.40794196712252262</v>
+      </c>
+    </row>
+    <row r="55" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>242</v>
       </c>
@@ -62037,8 +62535,20 @@
       <c r="EY55">
         <v>0.56696196687274403</v>
       </c>
-    </row>
-    <row r="56" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA55" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="FB55" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC55" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD55" s="6">
+        <v>0.47690400708159186</v>
+      </c>
+    </row>
+    <row r="56" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>243</v>
       </c>
@@ -62264,8 +62774,20 @@
       <c r="EY56">
         <v>0.43117737268274747</v>
       </c>
-    </row>
-    <row r="57" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA56" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="FB56" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC56" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD56" s="6">
+        <v>0.26647865242892721</v>
+      </c>
+    </row>
+    <row r="57" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>244</v>
       </c>
@@ -62491,8 +63013,20 @@
       <c r="EY57">
         <v>0.58972043561319354</v>
       </c>
-    </row>
-    <row r="58" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA57" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="FB57" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC57" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD57" s="6">
+        <v>0.26955292756620414</v>
+      </c>
+    </row>
+    <row r="58" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>245</v>
       </c>
@@ -62718,8 +63252,20 @@
       <c r="EY58">
         <v>0.44665383381091073</v>
       </c>
-    </row>
-    <row r="59" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA58" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="FB58" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC58" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD58" s="6">
+        <v>0.45496978287377421</v>
+      </c>
+    </row>
+    <row r="59" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>246</v>
       </c>
@@ -62945,8 +63491,20 @@
       <c r="EY59">
         <v>0.57211743382642732</v>
       </c>
-    </row>
-    <row r="60" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA59" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="FB59" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC59" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD59" s="6">
+        <v>0.45095439329121484</v>
+      </c>
+    </row>
+    <row r="60" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>247</v>
       </c>
@@ -63172,8 +63730,20 @@
       <c r="EY60">
         <v>0.43656617165324252</v>
       </c>
-    </row>
-    <row r="61" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA60" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="FB60" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC60" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD60" s="6">
+        <v>0.26982678075241878</v>
+      </c>
+    </row>
+    <row r="61" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>248</v>
       </c>
@@ -63399,8 +63969,20 @@
       <c r="EY61">
         <v>0.42882525256685156</v>
       </c>
-    </row>
-    <row r="62" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA61" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="FB61" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC61" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD61" s="6">
+        <v>0.32946096639945915</v>
+      </c>
+    </row>
+    <row r="62" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>249</v>
       </c>
@@ -63626,8 +64208,20 @@
       <c r="EY62">
         <v>0.40483671869102955</v>
       </c>
-    </row>
-    <row r="63" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA62" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="FB62" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC62" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD62" s="6">
+        <v>0.34056442041392671</v>
+      </c>
+    </row>
+    <row r="63" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>250</v>
       </c>
@@ -63853,8 +64447,20 @@
       <c r="EY63">
         <v>0.55608953192664634</v>
       </c>
-    </row>
-    <row r="64" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA63" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="FB63" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC63" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD63" s="6">
+        <v>0.21511655097552346</v>
+      </c>
+    </row>
+    <row r="64" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>251</v>
       </c>
@@ -64080,8 +64686,20 @@
       <c r="EY64">
         <v>0.62911171624600359</v>
       </c>
-    </row>
-    <row r="65" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA64" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="FB64" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC64" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD64" s="6">
+        <v>0.25571201740718436</v>
+      </c>
+    </row>
+    <row r="65" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>252</v>
       </c>
@@ -64307,8 +64925,20 @@
       <c r="EY65">
         <v>0.57307791374235451</v>
       </c>
-    </row>
-    <row r="66" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA65" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="FB65" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC65" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD65" s="6">
+        <v>0.37015933503149556</v>
+      </c>
+    </row>
+    <row r="66" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>253</v>
       </c>
@@ -64534,8 +65164,20 @@
       <c r="EY66">
         <v>0.56174687545374646</v>
       </c>
-    </row>
-    <row r="67" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA66" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="FB66" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC66" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD66" s="6">
+        <v>0.45058807759116437</v>
+      </c>
+    </row>
+    <row r="67" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>254</v>
       </c>
@@ -64761,8 +65403,20 @@
       <c r="EY67">
         <v>0.55969790392996577</v>
       </c>
-    </row>
-    <row r="68" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA67" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="FB67" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC67" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD67" s="6">
+        <v>0.35266034668292578</v>
+      </c>
+    </row>
+    <row r="68" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>255</v>
       </c>
@@ -64988,8 +65642,20 @@
       <c r="EY68">
         <v>0.3662947538900827</v>
       </c>
-    </row>
-    <row r="69" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA68" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="FB68" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC68" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD68" s="6">
+        <v>0.21885442440973776</v>
+      </c>
+    </row>
+    <row r="69" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>256</v>
       </c>
@@ -65215,8 +65881,20 @@
       <c r="EY69">
         <v>0.57022910677678085</v>
       </c>
-    </row>
-    <row r="70" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA69" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="FB69" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC69" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD69" s="6">
+        <v>0.40585383933609187</v>
+      </c>
+    </row>
+    <row r="70" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>257</v>
       </c>
@@ -65442,8 +66120,20 @@
       <c r="EY70">
         <v>0.5267177162644503</v>
       </c>
-    </row>
-    <row r="71" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA70" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="FB70" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC70" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD70" s="6">
+        <v>0.18542864969626882</v>
+      </c>
+    </row>
+    <row r="71" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>258</v>
       </c>
@@ -65669,8 +66359,20 @@
       <c r="EY71">
         <v>0.45346031670789072</v>
       </c>
-    </row>
-    <row r="72" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA71" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="FB71" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC71" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD71" s="6">
+        <v>0.48478168762149076</v>
+      </c>
+    </row>
+    <row r="72" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>259</v>
       </c>
@@ -65896,8 +66598,20 @@
       <c r="EY72">
         <v>0.50262550879793666</v>
       </c>
-    </row>
-    <row r="73" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA72" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="FB72" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC72" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD72" s="6">
+        <v>0.26018071254484076</v>
+      </c>
+    </row>
+    <row r="73" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>260</v>
       </c>
@@ -66123,8 +66837,20 @@
       <c r="EY73">
         <v>0.30319930452577354</v>
       </c>
-    </row>
-    <row r="74" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA73" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="FB73" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC73" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD73" s="6">
+        <v>0.2920886376334873</v>
+      </c>
+    </row>
+    <row r="74" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>261</v>
       </c>
@@ -66350,8 +67076,20 @@
       <c r="EY74">
         <v>0.1099435315205316</v>
       </c>
-    </row>
-    <row r="75" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA74" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="FB74" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC74" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD74" s="6">
+        <v>0.33212060457748077</v>
+      </c>
+    </row>
+    <row r="75" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>262</v>
       </c>
@@ -66577,8 +67315,20 @@
       <c r="EY75">
         <v>0.21931962207072853</v>
       </c>
-    </row>
-    <row r="76" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA75" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="FB75" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC75" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD75" s="6">
+        <v>0.30273696670158712</v>
+      </c>
+    </row>
+    <row r="76" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>263</v>
       </c>
@@ -66804,8 +67554,20 @@
       <c r="EY76">
         <v>0.15625931581155589</v>
       </c>
-    </row>
-    <row r="77" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA76" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="FB76" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC76" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD76" s="6">
+        <v>0.47262807843436089</v>
+      </c>
+    </row>
+    <row r="77" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>264</v>
       </c>
@@ -67031,8 +67793,20 @@
       <c r="EY77">
         <v>0.10003201381477303</v>
       </c>
-    </row>
-    <row r="78" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA77" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="FB77" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC77" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD77" s="6">
+        <v>0.43653873862653381</v>
+      </c>
+    </row>
+    <row r="78" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>265</v>
       </c>
@@ -67258,8 +68032,20 @@
       <c r="EY78">
         <v>0.15245304258652204</v>
       </c>
-    </row>
-    <row r="79" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA78" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="FB78" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC78" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD78" s="6">
+        <v>0.26725583429000915</v>
+      </c>
+    </row>
+    <row r="79" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>266</v>
       </c>
@@ -67485,8 +68271,20 @@
       <c r="EY79">
         <v>0.29521413455620538</v>
       </c>
-    </row>
-    <row r="80" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA79" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="FB79" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC79" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD79" s="6">
+        <v>0.2884872362697331</v>
+      </c>
+    </row>
+    <row r="80" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>267</v>
       </c>
@@ -67712,8 +68510,20 @@
       <c r="EY80">
         <v>6.7091698685272746E-2</v>
       </c>
-    </row>
-    <row r="81" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA80" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="FB80" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC80" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD80" s="6">
+        <v>0.38811816817984285</v>
+      </c>
+    </row>
+    <row r="81" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>268</v>
       </c>
@@ -67939,8 +68749,20 @@
       <c r="EY81">
         <v>0.27544765137897326</v>
       </c>
-    </row>
-    <row r="82" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA81" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="FB81" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC81" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD81" s="6">
+        <v>0.39058339119219243</v>
+      </c>
+    </row>
+    <row r="82" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>269</v>
       </c>
@@ -68166,8 +68988,20 @@
       <c r="EY82">
         <v>0.36289341789259283</v>
       </c>
-    </row>
-    <row r="83" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA82" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="FB82" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC82" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD82" s="6">
+        <v>0.40221238393013553</v>
+      </c>
+    </row>
+    <row r="83" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>270</v>
       </c>
@@ -68393,8 +69227,20 @@
       <c r="EY83">
         <v>0.10951060325389621</v>
       </c>
-    </row>
-    <row r="84" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA83" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="FB83" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC83" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD83" s="6">
+        <v>0.33785511190410528</v>
+      </c>
+    </row>
+    <row r="84" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>271</v>
       </c>
@@ -68620,8 +69466,20 @@
       <c r="EY84">
         <v>0.19631074510991139</v>
       </c>
-    </row>
-    <row r="85" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA84" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="FB84" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC84" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD84" s="6">
+        <v>0.38189459281511923</v>
+      </c>
+    </row>
+    <row r="85" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>272</v>
       </c>
@@ -68847,8 +69705,20 @@
       <c r="EY85">
         <v>0.22913310116966931</v>
       </c>
-    </row>
-    <row r="86" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA85" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="FB85" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC85" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD85" s="6">
+        <v>0.4446339701415204</v>
+      </c>
+    </row>
+    <row r="86" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>273</v>
       </c>
@@ -69074,8 +69944,20 @@
       <c r="EY86">
         <v>0.2727511464007879</v>
       </c>
-    </row>
-    <row r="87" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA86" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="FB86" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC86" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD86" s="6">
+        <v>0.48054204066235179</v>
+      </c>
+    </row>
+    <row r="87" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>274</v>
       </c>
@@ -69301,8 +70183,20 @@
       <c r="EY87">
         <v>0.1481467470601881</v>
       </c>
-    </row>
-    <row r="88" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA87" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="FB87" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC87" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD87" s="6">
+        <v>0.36390972516716358</v>
+      </c>
+    </row>
+    <row r="88" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>275</v>
       </c>
@@ -69528,8 +70422,20 @@
       <c r="EY88">
         <v>0.17463575962507921</v>
       </c>
-    </row>
-    <row r="89" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA88" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="FB88" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC88" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD88" s="6">
+        <v>0.64137700886171822</v>
+      </c>
+    </row>
+    <row r="89" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>276</v>
       </c>
@@ -69755,8 +70661,20 @@
       <c r="EY89">
         <v>0.35489657388215079</v>
       </c>
-    </row>
-    <row r="90" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA89" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="FB89" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC89" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD89" s="6">
+        <v>0.55774859105236285</v>
+      </c>
+    </row>
+    <row r="90" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
         <v>277</v>
       </c>
@@ -69982,8 +70900,20 @@
       <c r="EY90">
         <v>7.4766190977352973E-2</v>
       </c>
-    </row>
-    <row r="91" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA90" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="FB90" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC90" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD90" s="6">
+        <v>0.42263592301343023</v>
+      </c>
+    </row>
+    <row r="91" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>278</v>
       </c>
@@ -70209,8 +71139,20 @@
       <c r="EY91">
         <v>0.35341226324824154</v>
       </c>
-    </row>
-    <row r="92" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA91" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="FB91" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC91" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD91" s="6">
+        <v>0.4129060738169244</v>
+      </c>
+    </row>
+    <row r="92" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
         <v>279</v>
       </c>
@@ -70436,8 +71378,20 @@
       <c r="EY92">
         <v>0.16582252968609493</v>
       </c>
-    </row>
-    <row r="93" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA92" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="FB92" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC92" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD92" s="6">
+        <v>0.5411015944709231</v>
+      </c>
+    </row>
+    <row r="93" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
         <v>280</v>
       </c>
@@ -70663,8 +71617,20 @@
       <c r="EY93">
         <v>0.3146318441441186</v>
       </c>
-    </row>
-    <row r="94" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA93" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="FB93" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC93" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD93" s="6">
+        <v>0.53591732185357843</v>
+      </c>
+    </row>
+    <row r="94" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
         <v>281</v>
       </c>
@@ -70890,8 +71856,20 @@
       <c r="EY94">
         <v>0.34853255789301801</v>
       </c>
-    </row>
-    <row r="95" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA94" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="FB94" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC94" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD94" s="6">
+        <v>0.52882835465493849</v>
+      </c>
+    </row>
+    <row r="95" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
         <v>282</v>
       </c>
@@ -71117,8 +72095,20 @@
       <c r="EY95">
         <v>0.30280773521035043</v>
       </c>
-    </row>
-    <row r="96" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA95" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="FB95" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC95" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD95" s="6">
+        <v>0.47282338659439538</v>
+      </c>
+    </row>
+    <row r="96" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
         <v>283</v>
       </c>
@@ -71344,8 +72334,20 @@
       <c r="EY96">
         <v>0.47448657404498046</v>
       </c>
-    </row>
-    <row r="97" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA96" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="FB96" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC96" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD96" s="6">
+        <v>0.7208994211712163</v>
+      </c>
+    </row>
+    <row r="97" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
         <v>284</v>
       </c>
@@ -71571,8 +72573,20 @@
       <c r="EY97">
         <v>0.47199179679242631</v>
       </c>
-    </row>
-    <row r="98" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA97" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="FB97" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC97" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD97" s="6">
+        <v>0.741316639557561</v>
+      </c>
+    </row>
+    <row r="98" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
         <v>285</v>
       </c>
@@ -71798,8 +72812,20 @@
       <c r="EY98">
         <v>0.26803983283423705</v>
       </c>
-    </row>
-    <row r="99" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA98" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="FB98" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC98" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD98" s="6">
+        <v>0.6767036888309822</v>
+      </c>
+    </row>
+    <row r="99" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
         <v>286</v>
       </c>
@@ -72025,8 +73051,20 @@
       <c r="EY99">
         <v>0.29156594007432385</v>
       </c>
-    </row>
-    <row r="100" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA99" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="FB99" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC99" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD99" s="6">
+        <v>0.7470141803756889</v>
+      </c>
+    </row>
+    <row r="100" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
         <v>287</v>
       </c>
@@ -72252,8 +73290,20 @@
       <c r="EY100">
         <v>0.37598299965761045</v>
       </c>
-    </row>
-    <row r="101" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA100" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="FB100" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC100" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD100" s="6">
+        <v>0.59747138612810602</v>
+      </c>
+    </row>
+    <row r="101" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>288</v>
       </c>
@@ -72479,8 +73529,20 @@
       <c r="EY101">
         <v>0.34459749541590839</v>
       </c>
-    </row>
-    <row r="102" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA101" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="FB101" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC101" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD101" s="6">
+        <v>0.70450269845416558</v>
+      </c>
+    </row>
+    <row r="102" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>289</v>
       </c>
@@ -72706,8 +73768,20 @@
       <c r="EY102">
         <v>0.41209488913036596</v>
       </c>
-    </row>
-    <row r="103" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA102" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="FB102" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC102" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD102" s="6">
+        <v>0.54866612637150081</v>
+      </c>
+    </row>
+    <row r="103" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
         <v>290</v>
       </c>
@@ -72933,8 +74007,20 @@
       <c r="EY103">
         <v>0.34554536160696703</v>
       </c>
-    </row>
-    <row r="104" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA103" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="FB103" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC103" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD103" s="6">
+        <v>0.47863901695591982</v>
+      </c>
+    </row>
+    <row r="104" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
         <v>291</v>
       </c>
@@ -73160,8 +74246,20 @@
       <c r="EY104">
         <v>0.38748871919011618</v>
       </c>
-    </row>
-    <row r="105" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA104" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="FB104" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC104" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD104" s="6">
+        <v>0.53399736298429745</v>
+      </c>
+    </row>
+    <row r="105" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
         <v>292</v>
       </c>
@@ -73387,8 +74485,20 @@
       <c r="EY105">
         <v>0.43547166361134765</v>
       </c>
-    </row>
-    <row r="106" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA105" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="FB105" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC105" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD105" s="6">
+        <v>0.54114634382078586</v>
+      </c>
+    </row>
+    <row r="106" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
         <v>293</v>
       </c>
@@ -73614,8 +74724,20 @@
       <c r="EY106">
         <v>0.47152161402848247</v>
       </c>
-    </row>
-    <row r="107" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA106" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="FB106" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC106" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD106" s="6">
+        <v>0.6517149555216013</v>
+      </c>
+    </row>
+    <row r="107" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
         <v>294</v>
       </c>
@@ -73841,8 +74963,20 @@
       <c r="EY107">
         <v>0.31660429932341616</v>
       </c>
-    </row>
-    <row r="108" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA107" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="FB107" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC107" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD107" s="6">
+        <v>0.59684840383183613</v>
+      </c>
+    </row>
+    <row r="108" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
         <v>295</v>
       </c>
@@ -74068,8 +75202,20 @@
       <c r="EY108">
         <v>0.41591120077699301</v>
       </c>
-    </row>
-    <row r="109" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA108" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="FB108" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC108" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD108" s="6">
+        <v>0.62757018020669675</v>
+      </c>
+    </row>
+    <row r="109" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
         <v>296</v>
       </c>
@@ -74295,8 +75441,20 @@
       <c r="EY109">
         <v>0.39479718164051553</v>
       </c>
-    </row>
-    <row r="110" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA109" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="FB109" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC109" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD109" s="6">
+        <v>0.61963291815823551</v>
+      </c>
+    </row>
+    <row r="110" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
         <v>297</v>
       </c>
@@ -74522,8 +75680,20 @@
       <c r="EY110">
         <v>0.16005392343782679</v>
       </c>
-    </row>
-    <row r="111" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA110" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="FB110" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC110" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD110" s="6">
+        <v>0.47496387578658916</v>
+      </c>
+    </row>
+    <row r="111" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
         <v>298</v>
       </c>
@@ -74749,8 +75919,20 @@
       <c r="EY111">
         <v>0.17360007675359432</v>
       </c>
-    </row>
-    <row r="112" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA111" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="FB111" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC111" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD111" s="6">
+        <v>0.58860761780535853</v>
+      </c>
+    </row>
+    <row r="112" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
         <v>299</v>
       </c>
@@ -74976,8 +76158,20 @@
       <c r="EY112">
         <v>0.51785238110531195</v>
       </c>
-    </row>
-    <row r="113" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA112" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="FB112" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC112" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD112" s="6">
+        <v>0.56405360544578098</v>
+      </c>
+    </row>
+    <row r="113" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
         <v>300</v>
       </c>
@@ -75203,8 +76397,20 @@
       <c r="EY113">
         <v>0.47711268541441137</v>
       </c>
-    </row>
-    <row r="114" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA113" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="FB113" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC113" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD113" s="6">
+        <v>0.51616977443302303</v>
+      </c>
+    </row>
+    <row r="114" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
         <v>301</v>
       </c>
@@ -75430,8 +76636,20 @@
       <c r="EY114">
         <v>0.46983627372744519</v>
       </c>
-    </row>
-    <row r="115" spans="2:155" x14ac:dyDescent="0.45">
+      <c r="FA114" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="FB114" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC114" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD114" s="6">
+        <v>0.52548354068619618</v>
+      </c>
+    </row>
+    <row r="115" spans="2:160" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
         <v>302</v>
       </c>
@@ -75656,6 +76874,18 @@
       </c>
       <c r="EY115">
         <v>0.52585168479575928</v>
+      </c>
+      <c r="FA115" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="FB115" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="FC115" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="FD115" s="6">
+        <v>0.35977726384974823</v>
       </c>
     </row>
   </sheetData>
@@ -75676,7 +76906,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
         <v>54</v>
@@ -75699,7 +76929,7 @@
         <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -75713,7 +76943,7 @@
         <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
@@ -75727,7 +76957,7 @@
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -75741,7 +76971,7 @@
         <v>61</v>
       </c>
       <c r="E14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
@@ -75755,7 +76985,7 @@
         <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -75769,7 +76999,7 @@
         <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -75783,7 +77013,7 @@
         <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
@@ -75797,7 +77027,7 @@
         <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
@@ -75811,7 +77041,7 @@
         <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -75825,7 +77055,7 @@
         <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
@@ -75839,7 +77069,7 @@
         <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
@@ -75853,7 +77083,7 @@
         <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -75867,7 +77097,7 @@
         <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
@@ -75881,7 +77111,7 @@
         <v>71</v>
       </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -75895,7 +77125,7 @@
         <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
@@ -75909,7 +77139,7 @@
         <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
@@ -75923,7 +77153,7 @@
         <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
@@ -75937,7 +77167,7 @@
         <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
@@ -75951,7 +77181,7 @@
         <v>76</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
@@ -75965,7 +77195,7 @@
         <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
@@ -75979,7 +77209,7 @@
         <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -75993,7 +77223,7 @@
         <v>79</v>
       </c>
       <c r="E32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
@@ -76007,7 +77237,7 @@
         <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
@@ -76021,7 +77251,7 @@
         <v>81</v>
       </c>
       <c r="E34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
@@ -76035,7 +77265,7 @@
         <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
@@ -76049,7 +77279,7 @@
         <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
@@ -76063,7 +77293,7 @@
         <v>84</v>
       </c>
       <c r="E37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
@@ -76077,7 +77307,7 @@
         <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
@@ -76091,7 +77321,7 @@
         <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
@@ -76105,7 +77335,7 @@
         <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
@@ -76119,7 +77349,7 @@
         <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
@@ -76133,7 +77363,7 @@
         <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
@@ -76147,7 +77377,7 @@
         <v>90</v>
       </c>
       <c r="E43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
@@ -76161,7 +77391,7 @@
         <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
@@ -76175,7 +77405,7 @@
         <v>92</v>
       </c>
       <c r="E45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
@@ -76189,7 +77419,7 @@
         <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -76225,7 +77455,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C11" t="s">
         <v>57</v>
@@ -76236,7 +77466,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C12" t="s">
         <v>59</v>
@@ -76247,7 +77477,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C13" t="s">
         <v>60</v>
@@ -76258,7 +77488,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C14" t="s">
         <v>61</v>
@@ -76269,7 +77499,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
@@ -76280,7 +77510,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
@@ -76291,7 +77521,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C17" t="s">
         <v>64</v>
@@ -76302,7 +77532,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C18" t="s">
         <v>65</v>
@@ -76313,7 +77543,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C19" t="s">
         <v>66</v>
@@ -76324,7 +77554,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C20" t="s">
         <v>67</v>
@@ -76335,7 +77565,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -76346,7 +77576,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C22" t="s">
         <v>69</v>
@@ -76357,7 +77587,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C23" t="s">
         <v>70</v>
@@ -76368,7 +77598,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
         <v>71</v>
@@ -76379,7 +77609,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C25" t="s">
         <v>72</v>
@@ -76390,7 +77620,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
         <v>73</v>
@@ -76401,7 +77631,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
         <v>74</v>
@@ -76412,7 +77642,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C28" t="s">
         <v>75</v>
@@ -76423,7 +77653,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C29" t="s">
         <v>76</v>
@@ -76434,7 +77664,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
         <v>77</v>
@@ -76445,7 +77675,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
         <v>78</v>
@@ -76456,7 +77686,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -76467,7 +77697,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C33" t="s">
         <v>80</v>
@@ -76478,7 +77708,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C34" t="s">
         <v>81</v>
@@ -76489,7 +77719,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C35" t="s">
         <v>82</v>
@@ -76500,7 +77730,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C36" t="s">
         <v>83</v>
@@ -76511,7 +77741,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C37" t="s">
         <v>84</v>
@@ -76522,7 +77752,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C38" t="s">
         <v>85</v>
@@ -76533,7 +77763,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C39" t="s">
         <v>86</v>
@@ -76544,7 +77774,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C40" t="s">
         <v>87</v>
@@ -76555,7 +77785,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C41" t="s">
         <v>88</v>
@@ -76566,7 +77796,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C42" t="s">
         <v>89</v>
@@ -76577,7 +77807,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C43" t="s">
         <v>90</v>
@@ -76588,7 +77818,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
@@ -76599,7 +77829,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C45" t="s">
         <v>92</v>
@@ -76610,7 +77840,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C46" t="s">
         <v>93</v>
@@ -76621,7 +77851,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C47" t="s">
         <v>57</v>
@@ -76632,7 +77862,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s">
         <v>59</v>
@@ -76643,7 +77873,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C49" t="s">
         <v>60</v>
@@ -76654,7 +77884,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C50" t="s">
         <v>61</v>
@@ -76665,7 +77895,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C51" t="s">
         <v>62</v>
@@ -76676,7 +77906,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C52" t="s">
         <v>63</v>
@@ -76687,7 +77917,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C53" t="s">
         <v>64</v>
@@ -76698,7 +77928,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C54" t="s">
         <v>65</v>
@@ -76709,7 +77939,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C55" t="s">
         <v>66</v>
@@ -76720,7 +77950,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C56" t="s">
         <v>67</v>
@@ -76731,7 +77961,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C57" t="s">
         <v>68</v>
@@ -76742,7 +77972,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" t="s">
         <v>69</v>
@@ -76753,7 +77983,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" t="s">
         <v>70</v>
@@ -76764,7 +77994,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C60" t="s">
         <v>71</v>
@@ -76775,7 +78005,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C61" t="s">
         <v>72</v>
@@ -76786,7 +78016,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C62" t="s">
         <v>73</v>
@@ -76797,7 +78027,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C63" t="s">
         <v>74</v>
@@ -76808,7 +78038,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C64" t="s">
         <v>75</v>
@@ -76819,7 +78049,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C65" t="s">
         <v>76</v>
@@ -76830,7 +78060,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C66" t="s">
         <v>77</v>
@@ -76841,7 +78071,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C67" t="s">
         <v>78</v>
@@ -76852,7 +78082,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C68" t="s">
         <v>79</v>
@@ -76863,7 +78093,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C69" t="s">
         <v>80</v>
@@ -76874,7 +78104,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C70" t="s">
         <v>81</v>
@@ -76885,7 +78115,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C71" t="s">
         <v>82</v>
@@ -76896,7 +78126,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C72" t="s">
         <v>83</v>
@@ -76907,7 +78137,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C73" t="s">
         <v>84</v>
@@ -76918,7 +78148,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C74" t="s">
         <v>85</v>
@@ -76929,7 +78159,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C75" t="s">
         <v>86</v>
@@ -76940,7 +78170,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C76" t="s">
         <v>87</v>
@@ -76951,7 +78181,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C77" t="s">
         <v>88</v>
@@ -76962,7 +78192,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C78" t="s">
         <v>89</v>
@@ -76973,7 +78203,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
         <v>90</v>
@@ -76984,7 +78214,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C80" t="s">
         <v>91</v>
@@ -76995,7 +78225,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C81" t="s">
         <v>92</v>
@@ -77006,7 +78236,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C82" t="s">
         <v>93</v>
@@ -77039,7 +78269,7 @@
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
@@ -77456,16 +78686,16 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" t="s">
         <v>323</v>
-      </c>
-      <c r="E10" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
@@ -77479,7 +78709,7 @@
         <v>0.11636666666666666</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -77493,7 +78723,7 @@
         <v>0.14516666666666667</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
@@ -77507,7 +78737,7 @@
         <v>7.8466666666666671E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -77521,7 +78751,7 @@
         <v>0.11586666666666667</v>
       </c>
       <c r="E14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
@@ -77535,7 +78765,7 @@
         <v>0.63963333333333339</v>
       </c>
       <c r="E15" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -77549,7 +78779,7 @@
         <v>0.15053333333333332</v>
       </c>
       <c r="E16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -77563,7 +78793,7 @@
         <v>6.6333333333333341E-2</v>
       </c>
       <c r="E17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
@@ -77577,7 +78807,7 @@
         <v>0.11586666666666667</v>
       </c>
       <c r="E18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
@@ -77591,7 +78821,7 @@
         <v>0.73326666666666662</v>
       </c>
       <c r="E19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -77605,7 +78835,7 @@
         <v>0.71346666666666669</v>
       </c>
       <c r="E20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
@@ -77619,7 +78849,7 @@
         <v>0.1762</v>
       </c>
       <c r="E21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
@@ -77633,7 +78863,7 @@
         <v>0.28870000000000001</v>
       </c>
       <c r="E22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -77647,7 +78877,7 @@
         <v>0.31186666666666668</v>
       </c>
       <c r="E23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
@@ -77661,7 +78891,7 @@
         <v>0.36856666666666671</v>
       </c>
       <c r="E24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -77675,7 +78905,7 @@
         <v>0.17863333333333334</v>
       </c>
       <c r="E25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
@@ -77689,7 +78919,7 @@
         <v>0.11036666666666667</v>
       </c>
       <c r="E26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
@@ -77703,7 +78933,7 @@
         <v>0.32233333333333331</v>
       </c>
       <c r="E27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
@@ -77717,7 +78947,7 @@
         <v>0.32803333333333334</v>
       </c>
       <c r="E28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
@@ -77731,7 +78961,7 @@
         <v>0.19226666666666667</v>
       </c>
       <c r="E29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
@@ -77745,7 +78975,7 @@
         <v>0.20336666666666667</v>
       </c>
       <c r="E30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
@@ -77759,7 +78989,7 @@
         <v>0.34349999999999997</v>
       </c>
       <c r="E31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -77773,7 +79003,7 @@
         <v>0.20443333333333333</v>
       </c>
       <c r="E32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
@@ -77787,7 +79017,7 @@
         <v>0.11793333333333333</v>
       </c>
       <c r="E33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
@@ -77801,7 +79031,7 @@
         <v>6.409999999999999E-2</v>
       </c>
       <c r="E34" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
@@ -77815,7 +79045,7 @@
         <v>0.2733666666666667</v>
       </c>
       <c r="E35" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
@@ -77829,7 +79059,7 @@
         <v>0.37426666666666669</v>
       </c>
       <c r="E36" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
@@ -77843,7 +79073,7 @@
         <v>0.13460000000000003</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
@@ -77857,7 +79087,7 @@
         <v>0.12383333333333331</v>
       </c>
       <c r="E38" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
@@ -77871,7 +79101,7 @@
         <v>0.30443333333333333</v>
       </c>
       <c r="E39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
@@ -77885,7 +79115,7 @@
         <v>0.24256666666666662</v>
       </c>
       <c r="E40" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
@@ -77899,7 +79129,7 @@
         <v>0.11596666666666666</v>
       </c>
       <c r="E41" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
@@ -77913,7 +79143,7 @@
         <v>0.20236666666666667</v>
       </c>
       <c r="E42" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
@@ -77927,7 +79157,7 @@
         <v>0.39450000000000002</v>
       </c>
       <c r="E43" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
@@ -77941,7 +79171,7 @@
         <v>0.27323333333333338</v>
       </c>
       <c r="E44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
@@ -77955,7 +79185,7 @@
         <v>6.9066666666666665E-2</v>
       </c>
       <c r="E45" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
@@ -77969,7 +79199,7 @@
         <v>0.21983333333333333</v>
       </c>
       <c r="E46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
@@ -77983,7 +79213,7 @@
         <v>0.37340000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
@@ -77997,7 +79227,7 @@
         <v>0.23273333333333332</v>
       </c>
       <c r="E48" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -78011,7 +79241,7 @@
         <v>7.9899999999999999E-2</v>
       </c>
       <c r="E49" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
@@ -78025,7 +79255,7 @@
         <v>0.23929999999999998</v>
       </c>
       <c r="E50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
@@ -78039,7 +79269,7 @@
         <v>0.42853333333333338</v>
       </c>
       <c r="E51" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
@@ -78053,7 +79283,7 @@
         <v>0.3887666666666667</v>
       </c>
       <c r="E52" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
@@ -78067,7 +79297,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E53" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
@@ -78081,7 +79311,7 @@
         <v>0.13006666666666666</v>
       </c>
       <c r="E54" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
@@ -78095,7 +79325,7 @@
         <v>0.51756666666666662</v>
       </c>
       <c r="E55" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
@@ -78109,7 +79339,7 @@
         <v>0.37013333333333337</v>
       </c>
       <c r="E56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
@@ -78123,7 +79353,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="E57" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
@@ -78137,7 +79367,7 @@
         <v>0.25193333333333334</v>
       </c>
       <c r="E58" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
@@ -78151,7 +79381,7 @@
         <v>0.29743333333333338</v>
       </c>
       <c r="E59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
@@ -78165,7 +79395,7 @@
         <v>0.38220000000000004</v>
       </c>
       <c r="E60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
@@ -78179,7 +79409,7 @@
         <v>0.26450000000000001</v>
       </c>
       <c r="E61" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
@@ -78193,7 +79423,7 @@
         <v>0.20803333333333332</v>
       </c>
       <c r="E62" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
@@ -78207,7 +79437,7 @@
         <v>0.40710000000000002</v>
       </c>
       <c r="E63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
@@ -78221,7 +79451,7 @@
         <v>0.29320000000000002</v>
       </c>
       <c r="E64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
@@ -78235,7 +79465,7 @@
         <v>0.22930000000000003</v>
       </c>
       <c r="E65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
@@ -78249,7 +79479,7 @@
         <v>0.19296666666666665</v>
       </c>
       <c r="E66" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
@@ -78263,7 +79493,7 @@
         <v>0.4432666666666667</v>
       </c>
       <c r="E67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
@@ -78277,7 +79507,7 @@
         <v>0.37166666666666659</v>
       </c>
       <c r="E68" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
@@ -78291,7 +79521,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
@@ -78305,7 +79535,7 @@
         <v>5.4733333333333335E-2</v>
       </c>
       <c r="E70" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
@@ -78319,7 +79549,7 @@
         <v>0.42709999999999998</v>
       </c>
       <c r="E71" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
@@ -78333,7 +79563,7 @@
         <v>0.16689999999999997</v>
       </c>
       <c r="E72" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
@@ -78347,7 +79577,7 @@
         <v>0.16339999999999999</v>
       </c>
       <c r="E73" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
@@ -78361,7 +79591,7 @@
         <v>0.11469999999999998</v>
       </c>
       <c r="E74" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
@@ -78375,7 +79605,7 @@
         <v>0.25393333333333334</v>
       </c>
       <c r="E75" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
@@ -78389,7 +79619,7 @@
         <v>0.33733333333333332</v>
       </c>
       <c r="E76" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
@@ -78403,7 +79633,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E77" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
@@ -78417,7 +79647,7 @@
         <v>0.13589999999999999</v>
       </c>
       <c r="E78" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
@@ -78431,7 +79661,7 @@
         <v>0.29016666666666663</v>
       </c>
       <c r="E79" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
@@ -78445,7 +79675,7 @@
         <v>0.34273333333333333</v>
       </c>
       <c r="E80" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
@@ -78459,7 +79689,7 @@
         <v>0.11126666666666667</v>
       </c>
       <c r="E81" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
@@ -78473,7 +79703,7 @@
         <v>0.10056666666666665</v>
       </c>
       <c r="E82" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
@@ -78487,7 +79717,7 @@
         <v>0.37720000000000004</v>
       </c>
       <c r="E83" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
@@ -78501,7 +79731,7 @@
         <v>0.3926</v>
       </c>
       <c r="E84" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
@@ -78515,7 +79745,7 @@
         <v>0.1704</v>
       </c>
       <c r="E85" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
@@ -78529,7 +79759,7 @@
         <v>0.20269999999999999</v>
       </c>
       <c r="E86" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
@@ -78543,7 +79773,7 @@
         <v>0.26273333333333332</v>
       </c>
       <c r="E87" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
@@ -78557,7 +79787,7 @@
         <v>0.31196666666666667</v>
       </c>
       <c r="E88" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
@@ -78571,7 +79801,7 @@
         <v>0.1245</v>
       </c>
       <c r="E89" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
@@ -78585,7 +79815,7 @@
         <v>0.22923333333333332</v>
       </c>
       <c r="E90" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
@@ -78599,7 +79829,7 @@
         <v>0.28789999999999999</v>
       </c>
       <c r="E91" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
@@ -78613,7 +79843,7 @@
         <v>0.28363333333333335</v>
       </c>
       <c r="E92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
@@ -78627,7 +79857,7 @@
         <v>8.4766666666666657E-2</v>
       </c>
       <c r="E93" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
@@ -78641,7 +79871,7 @@
         <v>0.23056666666666667</v>
       </c>
       <c r="E94" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
@@ -78655,7 +79885,7 @@
         <v>0.33876666666666666</v>
       </c>
       <c r="E95" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
@@ -78669,7 +79899,7 @@
         <v>0.40139999999999998</v>
       </c>
       <c r="E96" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
@@ -78683,7 +79913,7 @@
         <v>0.10609999999999999</v>
       </c>
       <c r="E97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
@@ -78697,7 +79927,7 @@
         <v>0.12146666666666668</v>
       </c>
       <c r="E98" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
@@ -78711,7 +79941,7 @@
         <v>0.29856666666666665</v>
       </c>
       <c r="E99" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
@@ -78725,7 +79955,7 @@
         <v>0.12736666666666666</v>
       </c>
       <c r="E100" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
@@ -78739,7 +79969,7 @@
         <v>0.20493333333333333</v>
       </c>
       <c r="E101" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
@@ -78753,7 +79983,7 @@
         <v>0.18963333333333332</v>
       </c>
       <c r="E102" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.45">
@@ -78767,7 +79997,7 @@
         <v>0.36143333333333327</v>
       </c>
       <c r="E103" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.45">
@@ -78781,7 +80011,7 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="E104" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.45">
@@ -78795,7 +80025,7 @@
         <v>0.24406666666666665</v>
       </c>
       <c r="E105" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.45">
@@ -78809,7 +80039,7 @@
         <v>0.12663333333333335</v>
       </c>
       <c r="E106" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.45">
@@ -78823,7 +80053,7 @@
         <v>0.44693333333333335</v>
       </c>
       <c r="E107" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.45">
@@ -78837,7 +80067,7 @@
         <v>0.47516666666666668</v>
       </c>
       <c r="E108" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.45">
@@ -78851,7 +80081,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E109" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.45">
@@ -78865,7 +80095,7 @@
         <v>5.3266666666666664E-2</v>
       </c>
       <c r="E110" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.45">
@@ -78879,7 +80109,7 @@
         <v>0.47343333333333337</v>
       </c>
       <c r="E111" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.45">
@@ -78893,7 +80123,7 @@
         <v>0.43723333333333336</v>
       </c>
       <c r="E112" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.45">
@@ -78907,7 +80137,7 @@
         <v>0.16533333333333333</v>
       </c>
       <c r="E113" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.45">
@@ -78921,7 +80151,7 @@
         <v>0.23139999999999997</v>
       </c>
       <c r="E114" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.45">
@@ -78935,7 +80165,7 @@
         <v>0.32290000000000002</v>
       </c>
       <c r="E115" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.45">
@@ -78949,7 +80179,7 @@
         <v>0.37293333333333334</v>
       </c>
       <c r="E116" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.45">
@@ -78963,7 +80193,7 @@
         <v>0.29363333333333336</v>
       </c>
       <c r="E117" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.45">
@@ -78977,7 +80207,7 @@
         <v>0.14543333333333333</v>
       </c>
       <c r="E118" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.45">
@@ -78991,7 +80221,7 @@
         <v>0.39063333333333333</v>
       </c>
       <c r="E119" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.45">
@@ -79005,7 +80235,7 @@
         <v>0.12093333333333332</v>
       </c>
       <c r="E120" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.45">
@@ -79019,7 +80249,7 @@
         <v>9.8300000000000012E-2</v>
       </c>
       <c r="E121" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.45">
@@ -79033,7 +80263,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.45">
@@ -79047,7 +80277,7 @@
         <v>0.34403333333333336</v>
       </c>
       <c r="E123" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.45">
@@ -79061,7 +80291,7 @@
         <v>0.27913333333333329</v>
       </c>
       <c r="E124" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.45">
@@ -79075,7 +80305,7 @@
         <v>0.23246666666666668</v>
       </c>
       <c r="E125" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.45">
@@ -79089,7 +80319,7 @@
         <v>0.14909999999999998</v>
       </c>
       <c r="E126" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
